--- a/artfynd/A 47308-2025 artfynd.xlsx
+++ b/artfynd/A 47308-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60854797</v>
+        <v>292534</v>
       </c>
       <c r="B2" t="n">
-        <v>101215</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>103642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,20 +703,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Böke gård, 600 m väster, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445868.6935495895</v>
+        <v>445869</v>
       </c>
       <c r="R2" t="n">
-        <v>6184183.783071413</v>
+        <v>6184184</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -753,31 +754,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Igenväxt skogsgläntebacke.</t>
+          <t>2D7j1903. 3 små plantor, hårt trängda</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -785,15 +776,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>torr igenväxande gräsmark i skogsglänta</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Svensson</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Svensson</t>
+          <t>Via Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
